--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,112 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
-  <si>
-    <t>ArrowMakeupGuideUIForm.go</t>
-  </si>
-  <si>
-    <t>Vamos lá.</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip1</t>
-  </si>
-  <si>
-    <t>Acerte o jogo, Jogue por recompensas</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.tip2</t>
-  </si>
-  <si>
-    <t>Pronto para ganhar dinheiro!</t>
-  </si>
-  <si>
-    <t>ArrowMakeupGuideUIForm.Title</t>
-  </si>
-  <si>
-    <t>Guia do jogo</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.account</t>
-  </si>
-  <si>
-    <t>Conta</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.continue</t>
-  </si>
-  <si>
-    <t>Continuar</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.payment</t>
-  </si>
-  <si>
-    <t>Canal de pagamento</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.rebind</t>
-  </si>
-  <si>
-    <t>Rebind</t>
-  </si>
-  <si>
-    <t>ArrowMakeupInfoUIForm.tips</t>
-  </si>
-  <si>
-    <t>Dicas</t>
-  </si>
-  <si>
-    <t>ArrowMakeupOrdemUIForm.record</t>
-  </si>
-  <si>
-    <t>Retirar registro</t>
-  </si>
-  <si>
-    <t>ArrowMakeupTipsUIForm.Text_Title</t>
-  </si>
-  <si>
-    <t>Retirar instruções</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.makeup</t>
-  </si>
-  <si>
-    <t>Retirar</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.play</t>
-  </si>
-  <si>
-    <t>Ir para jogar</t>
-  </si>
-  <si>
-    <t>ArrowMakeuptItem.title</t>
-  </si>
-  <si>
-    <t>Requisitos de retirada</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.curBankInfo</t>
-  </si>
-  <si>
-    <t>Selecione um método de pagamento.</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relação de retirada: </t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.tile</t>
-  </si>
-  <si>
-    <t>ArrowMakeupUIForm.title_text</t>
-  </si>
-  <si>
-    <t>Equilíbrio</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -186,22 +81,10 @@
     <t>Selecione uma seta para apagar</t>
   </si>
   <si>
-    <t>ArrowMazeUIForm.ItemAutoRemoveFail</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>ArrowMazeUIForm.LevelTxt</t>
   </si>
   <si>
     <t>Nível {0}</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.makeuptxt</t>
-  </si>
-  <si>
-    <t>Colete {0} para retirar!</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -217,6 +100,9 @@
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.Continue</t>
+  </si>
+  <si>
+    <t>Continuar</t>
   </si>
   <si>
     <t>ArrowRewardDialogUIForm.NextLevel</t>
@@ -238,45 +124,6 @@
   </si>
   <si>
     <t>ArrowRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.claim</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardRewardUIForm.Notchanks</t>
-  </si>
-  <si>
-    <t>Não, obrigado.</t>
-  </si>
-  <si>
-    <t>ArrowScratchCardUIForm.check</t>
-  </si>
-  <si>
-    <t>Cartão de verificação</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.Confirm</t>
-  </si>
-  <si>
-    <t>Confirmação</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>Por favor, insira a sua conta {0}</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title</t>
-  </si>
-  <si>
-    <t>Método de retirada</t>
-  </si>
-  <si>
-    <t>ArrowSelectPaymentUIForm.title_1</t>
-  </si>
-  <si>
-    <t>Plataforma</t>
   </si>
   <si>
     <t>ArrowSettingController.OFF</t>
@@ -461,6 +308,12 @@
   <si>
     <t>Colete outro {0} para retirar</t>
   </si>
+  <si>
+    <t>TaskItem.infoTxt</t>
+  </si>
+  <si>
+    <t/>
+  </si>
 </sst>
 </file>
 
@@ -591,7 +444,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -599,19 +452,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -662,119 +515,15 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -788,6 +537,286 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -10408,2252 +10437,16 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1139">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1140">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1141">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1142">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1143">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1144">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1145">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1146">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1147">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1148">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1149">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1150">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1151">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1152">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1153">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1154">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1155">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1156">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1157">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1158">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1158"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1159">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1159"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>65</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1160">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1160"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>66</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>67</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A67" id="1161">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1161"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>67</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A68" id="1162">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1162"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1163">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1163"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1164">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1164"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="39.737557547433" customWidth="1"/>
+    <col min="2" max="2" width="34.0738721575056" customWidth="1"/>
     <col min="3" max="3" width="48.8264683314732" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12762,151 +10555,151 @@
         <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
@@ -12942,349 +10735,115 @@
         <v>60</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="0" t="s">
         <v>85</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="0" t="s">
-        <v>105</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="0" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="0" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="0" t="s">
-        <v>117</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="0" t="s">
-        <v>121</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="0" t="s">
-        <v>123</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1"/>
-      <c r="B67" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="C67" s="0" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1"/>
-      <c r="B68" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="C68" s="0" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1"/>
-      <c r="B69" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="C69" s="0" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1"/>
-      <c r="B70" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="C70" s="0" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -13296,7 +10855,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1438" name="A1">
+            <control shapeId="1095" r:id="rId1507" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13318,7 +10877,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1439" name="A2">
+            <control shapeId="1096" r:id="rId1508" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13340,7 +10899,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1440" name="A3">
+            <control shapeId="1097" r:id="rId1509" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13362,7 +10921,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1441" name="A4">
+            <control shapeId="1098" r:id="rId1510" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13384,7 +10943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1442" name="A5">
+            <control shapeId="1099" r:id="rId1511" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13406,7 +10965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1443" name="A6">
+            <control shapeId="1100" r:id="rId1512" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13428,7 +10987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1444" name="A7">
+            <control shapeId="1101" r:id="rId1513" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13450,7 +11009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1445" name="A8">
+            <control shapeId="1102" r:id="rId1514" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13472,7 +11031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1446" name="A9">
+            <control shapeId="1103" r:id="rId1515" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13494,7 +11053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1447" name="A10">
+            <control shapeId="1104" r:id="rId1516" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13516,7 +11075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1448" name="A11">
+            <control shapeId="1105" r:id="rId1517" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13538,7 +11097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1449" name="A12">
+            <control shapeId="1106" r:id="rId1518" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13560,7 +11119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1450" name="A13">
+            <control shapeId="1107" r:id="rId1519" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13582,7 +11141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1451" name="A14">
+            <control shapeId="1108" r:id="rId1520" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13604,7 +11163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1452" name="A15">
+            <control shapeId="1109" r:id="rId1521" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13626,7 +11185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1453" name="A16">
+            <control shapeId="1110" r:id="rId1522" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13648,7 +11207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1454" name="A17">
+            <control shapeId="1111" r:id="rId1523" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13670,7 +11229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1455" name="A18">
+            <control shapeId="1112" r:id="rId1524" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13692,7 +11251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1456" name="A19">
+            <control shapeId="1113" r:id="rId1525" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13714,7 +11273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1457" name="A20">
+            <control shapeId="1114" r:id="rId1526" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13736,7 +11295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1458" name="A21">
+            <control shapeId="1115" r:id="rId1527" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13758,7 +11317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1459" name="A22">
+            <control shapeId="1116" r:id="rId1528" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13780,7 +11339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1460" name="A23">
+            <control shapeId="1117" r:id="rId1529" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13802,7 +11361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1461" name="A24">
+            <control shapeId="1118" r:id="rId1530" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13824,7 +11383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1462" name="A25">
+            <control shapeId="1119" r:id="rId1531" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13846,7 +11405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1463" name="A26">
+            <control shapeId="1120" r:id="rId1532" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13868,7 +11427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1464" name="A27">
+            <control shapeId="1121" r:id="rId1533" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13890,7 +11449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1465" name="A28">
+            <control shapeId="1122" r:id="rId1534" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13912,7 +11471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1466" name="A29">
+            <control shapeId="1123" r:id="rId1535" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13934,7 +11493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1467" name="A30">
+            <control shapeId="1124" r:id="rId1536" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13956,7 +11515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1468" name="A31">
+            <control shapeId="1125" r:id="rId1537" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13978,7 +11537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1469" name="A32">
+            <control shapeId="1126" r:id="rId1538" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14000,7 +11559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1470" name="A33">
+            <control shapeId="1127" r:id="rId1539" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14022,7 +11581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1471" name="A34">
+            <control shapeId="1128" r:id="rId1540" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14044,7 +11603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1472" name="A35">
+            <control shapeId="1129" r:id="rId1541" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14066,7 +11625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1473" name="A36">
+            <control shapeId="1130" r:id="rId1542" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14088,7 +11647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1474" name="A37">
+            <control shapeId="1131" r:id="rId1543" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14110,7 +11669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1475" name="A38">
+            <control shapeId="1132" r:id="rId1544" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14132,7 +11691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1476" name="A39">
+            <control shapeId="1133" r:id="rId1545" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14154,7 +11713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1477" name="A40">
+            <control shapeId="1134" r:id="rId1546" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14176,7 +11735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1478" name="A41">
+            <control shapeId="1135" r:id="rId1547" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14198,7 +11757,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1479" name="A42">
+            <control shapeId="1136" r:id="rId1548" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14220,7 +11779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1480" name="A43">
+            <control shapeId="1137" r:id="rId1549" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14242,7 +11801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1481" name="A44">
+            <control shapeId="1138" r:id="rId1550" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -14262,578 +11821,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId1482" name="A45">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>44</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId1483" name="A46">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>45</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId1484" name="A47">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>46</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId1485" name="A48">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>47</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>48</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId1486" name="A49">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>48</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>49</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId1487" name="A50">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>49</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>50</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId1488" name="A51">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>50</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>51</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId1489" name="A52">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>51</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>52</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId1490" name="A53">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>52</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId1491" name="A54">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>53</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId1492" name="A55">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>54</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId1493" name="A56">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>55</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId1494" name="A57">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>56</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId1495" name="A58">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>57</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>58</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId1496" name="A59">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>58</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>59</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId1497" name="A60">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>59</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>60</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId1498" name="A61">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>60</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>61</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId1499" name="A62">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>61</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>62</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId1500" name="A63">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>62</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>63</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1158" r:id="rId1501" name="A64">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>63</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1159" r:id="rId1502" name="A65">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>64</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1160" r:id="rId1503" name="A66">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>65</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1161" r:id="rId1504" name="A67">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>66</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>67</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1162" r:id="rId1505" name="A68">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>67</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1163" r:id="rId1506" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1164" r:id="rId1507" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -309,10 +309,13 @@
     <t>Colete outro {0} para retirar</t>
   </si>
   <si>
-    <t>TaskItem.infoTxt</t>
+    <t>MakeupUIForm.title</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>TaskItem.infoTxt</t>
   </si>
 </sst>
 </file>
@@ -515,6 +518,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6654,6 +6661,182 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -6670,7 +6853,2243 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1095">
+            <xdr:cNvPr hidden="1" name="A1" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A2" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A3" id="1071">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A4" id="1072">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A5" id="1073">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A6" id="1074">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A7" id="1075">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A8" id="1076">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A9" id="1077">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A10" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A11" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A12" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A13" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A14" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A15" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1085">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1085"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1086">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1086"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1087">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1087"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1088">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1088"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1089">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1089"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1090">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1090"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -6745,18 +9164,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1096">
+            <xdr:cNvPr hidden="1" name="A28" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -6831,18 +9250,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1097">
+            <xdr:cNvPr hidden="1" name="A29" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -6917,18 +9336,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1098">
+            <xdr:cNvPr hidden="1" name="A30" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -7003,18 +9422,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1099">
+            <xdr:cNvPr hidden="1" name="A31" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -7089,18 +9508,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1100">
+            <xdr:cNvPr hidden="1" name="A32" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -7175,18 +9594,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1101">
+            <xdr:cNvPr hidden="1" name="A33" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -7261,18 +9680,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1102">
+            <xdr:cNvPr hidden="1" name="A34" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -7347,18 +9766,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1103">
+            <xdr:cNvPr hidden="1" name="A35" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -7433,18 +9852,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1104">
+            <xdr:cNvPr hidden="1" name="A36" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -7519,18 +9938,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1105">
+            <xdr:cNvPr hidden="1" name="A37" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -7605,18 +10024,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1106">
+            <xdr:cNvPr hidden="1" name="A38" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -7691,18 +10110,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1107">
+            <xdr:cNvPr hidden="1" name="A39" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -7777,18 +10196,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1108">
+            <xdr:cNvPr hidden="1" name="A40" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -7863,18 +10282,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1109">
+            <xdr:cNvPr hidden="1" name="A41" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -7949,18 +10368,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1110">
+            <xdr:cNvPr hidden="1" name="A42" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -8035,18 +10454,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1111">
+            <xdr:cNvPr hidden="1" name="A43" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -8121,18 +10540,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1112">
+            <xdr:cNvPr hidden="1" name="A44" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -8207,18 +10626,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1113">
+            <xdr:cNvPr hidden="1" name="A45" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -8287,2162 +10706,12 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1114">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1115">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1116">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1117">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1118">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1119">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1120">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1121">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1122">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1123">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1124">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1125">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1126">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1127">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1128">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1129">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1130">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1131">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1132">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1133">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1134">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1135">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1136">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1137">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1138">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -10846,6 +11115,15 @@
         <v>85</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -10855,7 +11133,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1507" name="A1">
+            <control shapeId="1069" r:id="rId1550" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10877,7 +11155,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1508" name="A2">
+            <control shapeId="1070" r:id="rId1551" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10899,7 +11177,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1509" name="A3">
+            <control shapeId="1071" r:id="rId1552" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10921,7 +11199,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1510" name="A4">
+            <control shapeId="1072" r:id="rId1553" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10943,7 +11221,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1511" name="A5">
+            <control shapeId="1073" r:id="rId1554" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10965,7 +11243,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1512" name="A6">
+            <control shapeId="1074" r:id="rId1555" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10987,7 +11265,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1513" name="A7">
+            <control shapeId="1075" r:id="rId1556" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11009,7 +11287,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1514" name="A8">
+            <control shapeId="1076" r:id="rId1557" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11031,7 +11309,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1515" name="A9">
+            <control shapeId="1077" r:id="rId1558" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11053,7 +11331,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1516" name="A10">
+            <control shapeId="1078" r:id="rId1559" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11075,7 +11353,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1517" name="A11">
+            <control shapeId="1079" r:id="rId1560" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11097,7 +11375,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1518" name="A12">
+            <control shapeId="1080" r:id="rId1561" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11119,7 +11397,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1519" name="A13">
+            <control shapeId="1081" r:id="rId1562" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11141,7 +11419,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1520" name="A14">
+            <control shapeId="1082" r:id="rId1563" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11163,7 +11441,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1521" name="A15">
+            <control shapeId="1083" r:id="rId1564" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11185,7 +11463,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1522" name="A16">
+            <control shapeId="1084" r:id="rId1565" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11207,7 +11485,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1523" name="A17">
+            <control shapeId="1085" r:id="rId1566" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11229,7 +11507,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1524" name="A18">
+            <control shapeId="1086" r:id="rId1567" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11251,7 +11529,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1525" name="A19">
+            <control shapeId="1087" r:id="rId1568" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11273,7 +11551,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1526" name="A20">
+            <control shapeId="1088" r:id="rId1569" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11295,7 +11573,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1527" name="A21">
+            <control shapeId="1089" r:id="rId1570" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11317,7 +11595,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1528" name="A22">
+            <control shapeId="1090" r:id="rId1571" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11339,7 +11617,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1529" name="A23">
+            <control shapeId="1091" r:id="rId1572" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11361,7 +11639,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1530" name="A24">
+            <control shapeId="1092" r:id="rId1573" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11383,7 +11661,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1531" name="A25">
+            <control shapeId="1093" r:id="rId1574" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11405,7 +11683,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1532" name="A26">
+            <control shapeId="1094" r:id="rId1575" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11427,7 +11705,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1533" name="A27">
+            <control shapeId="1095" r:id="rId1576" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11449,7 +11727,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId1534" name="A28">
+            <control shapeId="1096" r:id="rId1577" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11471,7 +11749,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId1535" name="A29">
+            <control shapeId="1097" r:id="rId1578" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11493,7 +11771,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId1536" name="A30">
+            <control shapeId="1098" r:id="rId1579" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11515,7 +11793,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId1537" name="A31">
+            <control shapeId="1099" r:id="rId1580" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11537,7 +11815,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId1538" name="A32">
+            <control shapeId="1100" r:id="rId1581" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11559,7 +11837,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId1539" name="A33">
+            <control shapeId="1101" r:id="rId1582" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11581,7 +11859,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId1540" name="A34">
+            <control shapeId="1102" r:id="rId1583" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11603,7 +11881,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId1541" name="A35">
+            <control shapeId="1103" r:id="rId1584" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11625,7 +11903,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId1542" name="A36">
+            <control shapeId="1104" r:id="rId1585" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11647,7 +11925,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId1543" name="A37">
+            <control shapeId="1105" r:id="rId1586" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11669,7 +11947,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId1544" name="A38">
+            <control shapeId="1106" r:id="rId1587" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11691,7 +11969,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId1545" name="A39">
+            <control shapeId="1107" r:id="rId1588" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11713,7 +11991,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId1546" name="A40">
+            <control shapeId="1108" r:id="rId1589" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11735,7 +12013,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId1547" name="A41">
+            <control shapeId="1109" r:id="rId1590" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11757,7 +12035,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId1548" name="A42">
+            <control shapeId="1110" r:id="rId1591" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11779,7 +12057,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId1549" name="A43">
+            <control shapeId="1111" r:id="rId1592" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11801,7 +12079,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId1550" name="A44">
+            <control shapeId="1112" r:id="rId1593" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11821,6 +12099,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1113" r:id="rId1594" name="A45">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>44</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -297,6 +297,15 @@
     <t>Lamentamos que a troca tenha falhado.</t>
   </si>
   <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
@@ -310,9 +319,6 @@
   </si>
   <si>
     <t>MakeupUIForm.title</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -507,11 +513,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,6 +525,14 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6837,6 +6851,370 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -6853,179 +7231,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1069">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1070">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1071">
+            <xdr:cNvPr hidden="1" name="A1" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1071"/>
@@ -7100,18 +7306,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1072">
+            <xdr:cNvPr hidden="1" name="A2" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -7186,18 +7392,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1073">
+            <xdr:cNvPr hidden="1" name="A3" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -7272,18 +7478,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1074">
+            <xdr:cNvPr hidden="1" name="A4" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -7358,18 +7564,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1075">
+            <xdr:cNvPr hidden="1" name="A5" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -7444,18 +7650,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1076">
+            <xdr:cNvPr hidden="1" name="A6" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -7530,18 +7736,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1077">
+            <xdr:cNvPr hidden="1" name="A7" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -7616,18 +7822,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1078">
+            <xdr:cNvPr hidden="1" name="A8" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -7702,18 +7908,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1079">
+            <xdr:cNvPr hidden="1" name="A9" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -7788,18 +7994,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1080">
+            <xdr:cNvPr hidden="1" name="A10" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -7874,18 +8080,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1081">
+            <xdr:cNvPr hidden="1" name="A11" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -7960,18 +8166,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1082">
+            <xdr:cNvPr hidden="1" name="A12" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -8046,18 +8252,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1083">
+            <xdr:cNvPr hidden="1" name="A13" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -8132,18 +8338,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1084">
+            <xdr:cNvPr hidden="1" name="A14" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -8218,18 +8424,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1085">
+            <xdr:cNvPr hidden="1" name="A15" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -8304,18 +8510,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1086">
+            <xdr:cNvPr hidden="1" name="A16" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -8390,18 +8596,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1087">
+            <xdr:cNvPr hidden="1" name="A17" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -8476,18 +8682,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1088">
+            <xdr:cNvPr hidden="1" name="A18" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -8562,18 +8768,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1089">
+            <xdr:cNvPr hidden="1" name="A19" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -8648,18 +8854,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1090">
+            <xdr:cNvPr hidden="1" name="A20" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -8734,18 +8940,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1091">
+            <xdr:cNvPr hidden="1" name="A21" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -8820,18 +9026,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1092">
+            <xdr:cNvPr hidden="1" name="A22" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -8906,18 +9112,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1093">
+            <xdr:cNvPr hidden="1" name="A23" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -8992,18 +9198,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1094">
+            <xdr:cNvPr hidden="1" name="A24" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9078,18 +9284,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1095">
+            <xdr:cNvPr hidden="1" name="A25" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9164,18 +9370,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1096">
+            <xdr:cNvPr hidden="1" name="A26" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9250,18 +9456,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1097">
+            <xdr:cNvPr hidden="1" name="A27" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9336,18 +9542,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1098">
+            <xdr:cNvPr hidden="1" name="A28" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9422,18 +9628,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1099">
+            <xdr:cNvPr hidden="1" name="A29" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9508,18 +9714,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1100">
+            <xdr:cNvPr hidden="1" name="A30" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -9594,18 +9800,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1101">
+            <xdr:cNvPr hidden="1" name="A31" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -9680,18 +9886,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1102">
+            <xdr:cNvPr hidden="1" name="A32" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -9766,18 +9972,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1103">
+            <xdr:cNvPr hidden="1" name="A33" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -9852,18 +10058,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1104">
+            <xdr:cNvPr hidden="1" name="A34" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -9938,18 +10144,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1105">
+            <xdr:cNvPr hidden="1" name="A35" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10024,18 +10230,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1106">
+            <xdr:cNvPr hidden="1" name="A36" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10110,18 +10316,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1107">
+            <xdr:cNvPr hidden="1" name="A37" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10196,18 +10402,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1108">
+            <xdr:cNvPr hidden="1" name="A38" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10282,18 +10488,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1109">
+            <xdr:cNvPr hidden="1" name="A39" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10368,18 +10574,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1110">
+            <xdr:cNvPr hidden="1" name="A40" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10454,18 +10660,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1111">
+            <xdr:cNvPr hidden="1" name="A41" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10540,18 +10746,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1112">
+            <xdr:cNvPr hidden="1" name="A42" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -10626,18 +10832,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1113">
+            <xdr:cNvPr hidden="1" name="A43" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -10706,12 +10912,356 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A44" id="1114">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1114"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A45" id="1115">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1115"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1116">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1116"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1117">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1117"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -11103,25 +11653,43 @@
         <v>82</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="0" t="s">
-        <v>85</v>
+    </row>
+    <row r="46">
+      <c r="A46" s="1"/>
+      <c r="B46" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1"/>
+      <c r="B47" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -11133,7 +11701,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId1550" name="A1">
+            <control shapeId="1071" r:id="rId1639" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11155,7 +11723,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId1551" name="A2">
+            <control shapeId="1072" r:id="rId1640" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11177,7 +11745,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId1552" name="A3">
+            <control shapeId="1073" r:id="rId1641" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11199,7 +11767,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId1553" name="A4">
+            <control shapeId="1074" r:id="rId1642" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11221,7 +11789,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1554" name="A5">
+            <control shapeId="1075" r:id="rId1643" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11243,7 +11811,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1555" name="A6">
+            <control shapeId="1076" r:id="rId1644" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11265,7 +11833,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1556" name="A7">
+            <control shapeId="1077" r:id="rId1645" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11287,7 +11855,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1557" name="A8">
+            <control shapeId="1078" r:id="rId1646" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11309,7 +11877,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1558" name="A9">
+            <control shapeId="1079" r:id="rId1647" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11331,7 +11899,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1559" name="A10">
+            <control shapeId="1080" r:id="rId1648" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11353,7 +11921,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1560" name="A11">
+            <control shapeId="1081" r:id="rId1649" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11375,7 +11943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1561" name="A12">
+            <control shapeId="1082" r:id="rId1650" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11397,7 +11965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1562" name="A13">
+            <control shapeId="1083" r:id="rId1651" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11419,7 +11987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1563" name="A14">
+            <control shapeId="1084" r:id="rId1652" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11441,7 +12009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1564" name="A15">
+            <control shapeId="1085" r:id="rId1653" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11463,7 +12031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1565" name="A16">
+            <control shapeId="1086" r:id="rId1654" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11485,7 +12053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1566" name="A17">
+            <control shapeId="1087" r:id="rId1655" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11507,7 +12075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1567" name="A18">
+            <control shapeId="1088" r:id="rId1656" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11529,7 +12097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1568" name="A19">
+            <control shapeId="1089" r:id="rId1657" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11551,7 +12119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1569" name="A20">
+            <control shapeId="1090" r:id="rId1658" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11573,7 +12141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1570" name="A21">
+            <control shapeId="1091" r:id="rId1659" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11595,7 +12163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1571" name="A22">
+            <control shapeId="1092" r:id="rId1660" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11617,7 +12185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1572" name="A23">
+            <control shapeId="1093" r:id="rId1661" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11639,7 +12207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1573" name="A24">
+            <control shapeId="1094" r:id="rId1662" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11661,7 +12229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1574" name="A25">
+            <control shapeId="1095" r:id="rId1663" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11683,7 +12251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1575" name="A26">
+            <control shapeId="1096" r:id="rId1664" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11705,7 +12273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1576" name="A27">
+            <control shapeId="1097" r:id="rId1665" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11727,7 +12295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1577" name="A28">
+            <control shapeId="1098" r:id="rId1666" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11749,7 +12317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1578" name="A29">
+            <control shapeId="1099" r:id="rId1667" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11771,7 +12339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1579" name="A30">
+            <control shapeId="1100" r:id="rId1668" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11793,7 +12361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1580" name="A31">
+            <control shapeId="1101" r:id="rId1669" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11815,7 +12383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1581" name="A32">
+            <control shapeId="1102" r:id="rId1670" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11837,7 +12405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1582" name="A33">
+            <control shapeId="1103" r:id="rId1671" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11859,7 +12427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1583" name="A34">
+            <control shapeId="1104" r:id="rId1672" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11881,7 +12449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1584" name="A35">
+            <control shapeId="1105" r:id="rId1673" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11903,7 +12471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1585" name="A36">
+            <control shapeId="1106" r:id="rId1674" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11925,7 +12493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1586" name="A37">
+            <control shapeId="1107" r:id="rId1675" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11947,7 +12515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1587" name="A38">
+            <control shapeId="1108" r:id="rId1676" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11969,7 +12537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1588" name="A39">
+            <control shapeId="1109" r:id="rId1677" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11991,7 +12559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1589" name="A40">
+            <control shapeId="1110" r:id="rId1678" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12013,7 +12581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1590" name="A41">
+            <control shapeId="1111" r:id="rId1679" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12035,7 +12603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1591" name="A42">
+            <control shapeId="1112" r:id="rId1680" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12057,7 +12625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1592" name="A43">
+            <control shapeId="1113" r:id="rId1681" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12079,7 +12647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1593" name="A44">
+            <control shapeId="1114" r:id="rId1682" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12101,7 +12669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1594" name="A45">
+            <control shapeId="1115" r:id="rId1683" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12121,6 +12689,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1116" r:id="rId1684" name="A46">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>45</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>46</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1117" r:id="rId1685" name="A47">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>46</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -321,6 +321,9 @@
     <t>MakeupUIForm.title</t>
   </si>
   <si>
+    <t>PrelevelUIForm.txtLevel</t>
+  </si>
+  <si>
     <t>TaskItem.infoTxt</t>
   </si>
 </sst>
@@ -536,6 +539,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7215,6 +7222,194 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7231,93 +7426,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1071">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1072">
+            <xdr:cNvPr hidden="1" name="A1" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1072"/>
@@ -7392,18 +7501,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1073">
+            <xdr:cNvPr hidden="1" name="A2" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -7478,18 +7587,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1074">
+            <xdr:cNvPr hidden="1" name="A3" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -7564,18 +7673,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1075">
+            <xdr:cNvPr hidden="1" name="A4" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -7650,18 +7759,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1076">
+            <xdr:cNvPr hidden="1" name="A5" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -7736,18 +7845,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1077">
+            <xdr:cNvPr hidden="1" name="A6" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -7822,18 +7931,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1078">
+            <xdr:cNvPr hidden="1" name="A7" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -7908,18 +8017,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1079">
+            <xdr:cNvPr hidden="1" name="A8" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -7994,18 +8103,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1080">
+            <xdr:cNvPr hidden="1" name="A9" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -8080,18 +8189,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1081">
+            <xdr:cNvPr hidden="1" name="A10" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -8166,18 +8275,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1082">
+            <xdr:cNvPr hidden="1" name="A11" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -8252,18 +8361,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1083">
+            <xdr:cNvPr hidden="1" name="A12" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -8338,18 +8447,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1084">
+            <xdr:cNvPr hidden="1" name="A13" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -8424,18 +8533,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1085">
+            <xdr:cNvPr hidden="1" name="A14" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -8510,18 +8619,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1086">
+            <xdr:cNvPr hidden="1" name="A15" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -8596,18 +8705,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1087">
+            <xdr:cNvPr hidden="1" name="A16" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -8682,18 +8791,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1088">
+            <xdr:cNvPr hidden="1" name="A17" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -8768,18 +8877,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1089">
+            <xdr:cNvPr hidden="1" name="A18" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -8854,18 +8963,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1090">
+            <xdr:cNvPr hidden="1" name="A19" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -8940,18 +9049,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1091">
+            <xdr:cNvPr hidden="1" name="A20" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -9026,18 +9135,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1092">
+            <xdr:cNvPr hidden="1" name="A21" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9112,18 +9221,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1093">
+            <xdr:cNvPr hidden="1" name="A22" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9198,18 +9307,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1094">
+            <xdr:cNvPr hidden="1" name="A23" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9284,18 +9393,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1095">
+            <xdr:cNvPr hidden="1" name="A24" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9370,18 +9479,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1096">
+            <xdr:cNvPr hidden="1" name="A25" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9456,18 +9565,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1097">
+            <xdr:cNvPr hidden="1" name="A26" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9542,18 +9651,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1098">
+            <xdr:cNvPr hidden="1" name="A27" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9628,18 +9737,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1099">
+            <xdr:cNvPr hidden="1" name="A28" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9714,18 +9823,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1100">
+            <xdr:cNvPr hidden="1" name="A29" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -9800,18 +9909,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1101">
+            <xdr:cNvPr hidden="1" name="A30" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -9886,18 +9995,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1102">
+            <xdr:cNvPr hidden="1" name="A31" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -9972,18 +10081,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1103">
+            <xdr:cNvPr hidden="1" name="A32" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10058,18 +10167,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1104">
+            <xdr:cNvPr hidden="1" name="A33" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10144,18 +10253,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1105">
+            <xdr:cNvPr hidden="1" name="A34" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10230,18 +10339,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1106">
+            <xdr:cNvPr hidden="1" name="A35" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10316,18 +10425,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1107">
+            <xdr:cNvPr hidden="1" name="A36" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10402,18 +10511,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1108">
+            <xdr:cNvPr hidden="1" name="A37" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10488,18 +10597,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1109">
+            <xdr:cNvPr hidden="1" name="A38" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10574,18 +10683,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1110">
+            <xdr:cNvPr hidden="1" name="A39" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10660,18 +10769,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1111">
+            <xdr:cNvPr hidden="1" name="A40" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10746,18 +10855,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1112">
+            <xdr:cNvPr hidden="1" name="A41" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -10832,18 +10941,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1113">
+            <xdr:cNvPr hidden="1" name="A42" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -10918,18 +11027,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1114">
+            <xdr:cNvPr hidden="1" name="A43" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11004,18 +11113,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1115">
+            <xdr:cNvPr hidden="1" name="A44" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11090,18 +11199,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1116">
+            <xdr:cNvPr hidden="1" name="A45" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11176,18 +11285,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1117">
+            <xdr:cNvPr hidden="1" name="A46" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11256,12 +11365,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1118">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1118"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1119">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1119"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -11692,6 +11973,15 @@
         <v>81</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="1"/>
+      <c r="B48" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -11701,7 +11991,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId1639" name="A1">
+            <control shapeId="1072" r:id="rId1685" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11723,7 +12013,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId1640" name="A2">
+            <control shapeId="1073" r:id="rId1686" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11745,7 +12035,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1641" name="A3">
+            <control shapeId="1074" r:id="rId1687" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11767,7 +12057,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1642" name="A4">
+            <control shapeId="1075" r:id="rId1688" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11789,7 +12079,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1643" name="A5">
+            <control shapeId="1076" r:id="rId1689" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11811,7 +12101,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1644" name="A6">
+            <control shapeId="1077" r:id="rId1690" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11833,7 +12123,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1645" name="A7">
+            <control shapeId="1078" r:id="rId1691" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11855,7 +12145,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1646" name="A8">
+            <control shapeId="1079" r:id="rId1692" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11877,7 +12167,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1647" name="A9">
+            <control shapeId="1080" r:id="rId1693" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11899,7 +12189,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1648" name="A10">
+            <control shapeId="1081" r:id="rId1694" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11921,7 +12211,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1649" name="A11">
+            <control shapeId="1082" r:id="rId1695" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11943,7 +12233,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1650" name="A12">
+            <control shapeId="1083" r:id="rId1696" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11965,7 +12255,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1651" name="A13">
+            <control shapeId="1084" r:id="rId1697" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11987,7 +12277,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1652" name="A14">
+            <control shapeId="1085" r:id="rId1698" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12009,7 +12299,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1653" name="A15">
+            <control shapeId="1086" r:id="rId1699" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12031,7 +12321,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1654" name="A16">
+            <control shapeId="1087" r:id="rId1700" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12053,7 +12343,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1655" name="A17">
+            <control shapeId="1088" r:id="rId1701" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12075,7 +12365,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1656" name="A18">
+            <control shapeId="1089" r:id="rId1702" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12097,7 +12387,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1657" name="A19">
+            <control shapeId="1090" r:id="rId1703" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12119,7 +12409,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1658" name="A20">
+            <control shapeId="1091" r:id="rId1704" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12141,7 +12431,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1659" name="A21">
+            <control shapeId="1092" r:id="rId1705" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12163,7 +12453,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1660" name="A22">
+            <control shapeId="1093" r:id="rId1706" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12185,7 +12475,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1661" name="A23">
+            <control shapeId="1094" r:id="rId1707" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12207,7 +12497,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1662" name="A24">
+            <control shapeId="1095" r:id="rId1708" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12229,7 +12519,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1663" name="A25">
+            <control shapeId="1096" r:id="rId1709" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12251,7 +12541,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1664" name="A26">
+            <control shapeId="1097" r:id="rId1710" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12273,7 +12563,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1665" name="A27">
+            <control shapeId="1098" r:id="rId1711" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12295,7 +12585,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1666" name="A28">
+            <control shapeId="1099" r:id="rId1712" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12317,7 +12607,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1667" name="A29">
+            <control shapeId="1100" r:id="rId1713" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12339,7 +12629,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1668" name="A30">
+            <control shapeId="1101" r:id="rId1714" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12361,7 +12651,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1669" name="A31">
+            <control shapeId="1102" r:id="rId1715" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12383,7 +12673,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1670" name="A32">
+            <control shapeId="1103" r:id="rId1716" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12405,7 +12695,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1671" name="A33">
+            <control shapeId="1104" r:id="rId1717" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12427,7 +12717,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1672" name="A34">
+            <control shapeId="1105" r:id="rId1718" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12449,7 +12739,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1673" name="A35">
+            <control shapeId="1106" r:id="rId1719" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12471,7 +12761,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1674" name="A36">
+            <control shapeId="1107" r:id="rId1720" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12493,7 +12783,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1675" name="A37">
+            <control shapeId="1108" r:id="rId1721" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12515,7 +12805,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1676" name="A38">
+            <control shapeId="1109" r:id="rId1722" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12537,7 +12827,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1677" name="A39">
+            <control shapeId="1110" r:id="rId1723" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12559,7 +12849,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1678" name="A40">
+            <control shapeId="1111" r:id="rId1724" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12581,7 +12871,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1679" name="A41">
+            <control shapeId="1112" r:id="rId1725" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12603,7 +12893,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1680" name="A42">
+            <control shapeId="1113" r:id="rId1726" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12625,7 +12915,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1681" name="A43">
+            <control shapeId="1114" r:id="rId1727" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12647,7 +12937,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1682" name="A44">
+            <control shapeId="1115" r:id="rId1728" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12669,7 +12959,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1683" name="A45">
+            <control shapeId="1116" r:id="rId1729" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12691,7 +12981,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1684" name="A46">
+            <control shapeId="1117" r:id="rId1730" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12713,7 +13003,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1685" name="A47">
+            <control shapeId="1118" r:id="rId1731" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12733,6 +13023,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1119" r:id="rId1732" name="A48">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>47</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -321,6 +321,9 @@
     <t>MakeupUIForm.title</t>
   </si>
   <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
@@ -543,6 +546,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7410,6 +7417,198 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7426,93 +7625,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1072">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1073">
+            <xdr:cNvPr hidden="1" name="A1" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1073"/>
@@ -7587,18 +7700,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1074">
+            <xdr:cNvPr hidden="1" name="A2" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1074"/>
@@ -7673,18 +7786,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1075">
+            <xdr:cNvPr hidden="1" name="A3" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1075"/>
@@ -7759,18 +7872,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1076">
+            <xdr:cNvPr hidden="1" name="A4" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1076"/>
@@ -7845,18 +7958,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1077">
+            <xdr:cNvPr hidden="1" name="A5" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1077"/>
@@ -7931,18 +8044,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1078">
+            <xdr:cNvPr hidden="1" name="A6" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1078"/>
@@ -8017,18 +8130,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1079">
+            <xdr:cNvPr hidden="1" name="A7" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1079"/>
@@ -8103,18 +8216,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1080">
+            <xdr:cNvPr hidden="1" name="A8" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1080"/>
@@ -8189,18 +8302,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1081">
+            <xdr:cNvPr hidden="1" name="A9" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1081"/>
@@ -8275,18 +8388,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1082">
+            <xdr:cNvPr hidden="1" name="A10" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1082"/>
@@ -8361,18 +8474,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1083">
+            <xdr:cNvPr hidden="1" name="A11" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1083"/>
@@ -8447,18 +8560,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1084">
+            <xdr:cNvPr hidden="1" name="A12" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1084"/>
@@ -8533,18 +8646,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1085">
+            <xdr:cNvPr hidden="1" name="A13" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1085"/>
@@ -8619,18 +8732,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1086">
+            <xdr:cNvPr hidden="1" name="A14" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1086"/>
@@ -8705,18 +8818,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1087">
+            <xdr:cNvPr hidden="1" name="A15" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1087"/>
@@ -8791,18 +8904,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1088">
+            <xdr:cNvPr hidden="1" name="A16" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1088"/>
@@ -8877,18 +8990,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1089">
+            <xdr:cNvPr hidden="1" name="A17" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1089"/>
@@ -8963,18 +9076,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1090">
+            <xdr:cNvPr hidden="1" name="A18" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -9049,18 +9162,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1091">
+            <xdr:cNvPr hidden="1" name="A19" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -9135,18 +9248,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1092">
+            <xdr:cNvPr hidden="1" name="A20" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9221,18 +9334,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1093">
+            <xdr:cNvPr hidden="1" name="A21" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9307,18 +9420,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1094">
+            <xdr:cNvPr hidden="1" name="A22" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9393,18 +9506,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1095">
+            <xdr:cNvPr hidden="1" name="A23" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9479,18 +9592,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1096">
+            <xdr:cNvPr hidden="1" name="A24" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9565,18 +9678,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1097">
+            <xdr:cNvPr hidden="1" name="A25" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9651,18 +9764,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1098">
+            <xdr:cNvPr hidden="1" name="A26" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9737,18 +9850,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1099">
+            <xdr:cNvPr hidden="1" name="A27" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9823,18 +9936,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1100">
+            <xdr:cNvPr hidden="1" name="A28" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -9909,18 +10022,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1101">
+            <xdr:cNvPr hidden="1" name="A29" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -9995,18 +10108,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1102">
+            <xdr:cNvPr hidden="1" name="A30" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10081,18 +10194,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1103">
+            <xdr:cNvPr hidden="1" name="A31" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10167,18 +10280,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1104">
+            <xdr:cNvPr hidden="1" name="A32" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10253,18 +10366,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1105">
+            <xdr:cNvPr hidden="1" name="A33" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10339,18 +10452,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1106">
+            <xdr:cNvPr hidden="1" name="A34" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10425,18 +10538,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1107">
+            <xdr:cNvPr hidden="1" name="A35" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10511,18 +10624,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1108">
+            <xdr:cNvPr hidden="1" name="A36" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10597,18 +10710,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1109">
+            <xdr:cNvPr hidden="1" name="A37" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10683,18 +10796,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1110">
+            <xdr:cNvPr hidden="1" name="A38" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10769,18 +10882,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1111">
+            <xdr:cNvPr hidden="1" name="A39" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10855,18 +10968,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1112">
+            <xdr:cNvPr hidden="1" name="A40" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -10941,18 +11054,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1113">
+            <xdr:cNvPr hidden="1" name="A41" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11027,18 +11140,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1114">
+            <xdr:cNvPr hidden="1" name="A42" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11113,18 +11226,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1115">
+            <xdr:cNvPr hidden="1" name="A43" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11199,18 +11312,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1116">
+            <xdr:cNvPr hidden="1" name="A44" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11285,18 +11398,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1117">
+            <xdr:cNvPr hidden="1" name="A45" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11371,18 +11484,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1118">
+            <xdr:cNvPr hidden="1" name="A46" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -11457,18 +11570,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1119">
+            <xdr:cNvPr hidden="1" name="A47" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -11537,12 +11650,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1120">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1120"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A49" id="1121">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1121"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -11982,6 +12267,15 @@
         <v>81</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1"/>
+      <c r="B49" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -11991,7 +12285,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId1685" name="A1">
+            <control shapeId="1073" r:id="rId1732" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12013,7 +12307,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1686" name="A2">
+            <control shapeId="1074" r:id="rId1733" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12035,7 +12329,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1687" name="A3">
+            <control shapeId="1075" r:id="rId1734" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12057,7 +12351,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1688" name="A4">
+            <control shapeId="1076" r:id="rId1735" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12079,7 +12373,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1689" name="A5">
+            <control shapeId="1077" r:id="rId1736" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12101,7 +12395,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1690" name="A6">
+            <control shapeId="1078" r:id="rId1737" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12123,7 +12417,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1691" name="A7">
+            <control shapeId="1079" r:id="rId1738" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12145,7 +12439,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1692" name="A8">
+            <control shapeId="1080" r:id="rId1739" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12167,7 +12461,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1693" name="A9">
+            <control shapeId="1081" r:id="rId1740" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12189,7 +12483,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1694" name="A10">
+            <control shapeId="1082" r:id="rId1741" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12211,7 +12505,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1695" name="A11">
+            <control shapeId="1083" r:id="rId1742" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12233,7 +12527,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1696" name="A12">
+            <control shapeId="1084" r:id="rId1743" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12255,7 +12549,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1697" name="A13">
+            <control shapeId="1085" r:id="rId1744" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12277,7 +12571,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1698" name="A14">
+            <control shapeId="1086" r:id="rId1745" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12299,7 +12593,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1699" name="A15">
+            <control shapeId="1087" r:id="rId1746" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12321,7 +12615,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1700" name="A16">
+            <control shapeId="1088" r:id="rId1747" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12343,7 +12637,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1701" name="A17">
+            <control shapeId="1089" r:id="rId1748" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12365,7 +12659,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1702" name="A18">
+            <control shapeId="1090" r:id="rId1749" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12387,7 +12681,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1703" name="A19">
+            <control shapeId="1091" r:id="rId1750" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12409,7 +12703,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1704" name="A20">
+            <control shapeId="1092" r:id="rId1751" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12431,7 +12725,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1705" name="A21">
+            <control shapeId="1093" r:id="rId1752" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12453,7 +12747,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1706" name="A22">
+            <control shapeId="1094" r:id="rId1753" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12475,7 +12769,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1707" name="A23">
+            <control shapeId="1095" r:id="rId1754" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12497,7 +12791,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1708" name="A24">
+            <control shapeId="1096" r:id="rId1755" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12519,7 +12813,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1709" name="A25">
+            <control shapeId="1097" r:id="rId1756" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12541,7 +12835,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1710" name="A26">
+            <control shapeId="1098" r:id="rId1757" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12563,7 +12857,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1711" name="A27">
+            <control shapeId="1099" r:id="rId1758" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12585,7 +12879,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1712" name="A28">
+            <control shapeId="1100" r:id="rId1759" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12607,7 +12901,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1713" name="A29">
+            <control shapeId="1101" r:id="rId1760" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12629,7 +12923,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1714" name="A30">
+            <control shapeId="1102" r:id="rId1761" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12651,7 +12945,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1715" name="A31">
+            <control shapeId="1103" r:id="rId1762" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12673,7 +12967,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1716" name="A32">
+            <control shapeId="1104" r:id="rId1763" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12695,7 +12989,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1717" name="A33">
+            <control shapeId="1105" r:id="rId1764" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12717,7 +13011,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1718" name="A34">
+            <control shapeId="1106" r:id="rId1765" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12739,7 +13033,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1719" name="A35">
+            <control shapeId="1107" r:id="rId1766" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12761,7 +13055,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1720" name="A36">
+            <control shapeId="1108" r:id="rId1767" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12783,7 +13077,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1721" name="A37">
+            <control shapeId="1109" r:id="rId1768" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12805,7 +13099,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1722" name="A38">
+            <control shapeId="1110" r:id="rId1769" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12827,7 +13121,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1723" name="A39">
+            <control shapeId="1111" r:id="rId1770" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12849,7 +13143,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1724" name="A40">
+            <control shapeId="1112" r:id="rId1771" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12871,7 +13165,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1725" name="A41">
+            <control shapeId="1113" r:id="rId1772" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12893,7 +13187,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1726" name="A42">
+            <control shapeId="1114" r:id="rId1773" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12915,7 +13209,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1727" name="A43">
+            <control shapeId="1115" r:id="rId1774" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12937,7 +13231,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1728" name="A44">
+            <control shapeId="1116" r:id="rId1775" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12959,7 +13253,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1729" name="A45">
+            <control shapeId="1117" r:id="rId1776" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12981,7 +13275,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1730" name="A46">
+            <control shapeId="1118" r:id="rId1777" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13003,7 +13297,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1731" name="A47">
+            <control shapeId="1119" r:id="rId1778" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13025,7 +13319,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1732" name="A48">
+            <control shapeId="1120" r:id="rId1779" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13045,6 +13339,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1121" r:id="rId1780" name="A49">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,7 +55,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+  <si>
+    <t>AddBallsUIForm.ballTxt</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>AddBallsUIForm.continueTxt</t>
+  </si>
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -73,18 +82,6 @@
   </si>
   <si>
     <t>Reviver</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.elimanateHit</t>
-  </si>
-  <si>
-    <t>Selecione uma seta para apagar</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.LevelTxt</t>
-  </si>
-  <si>
-    <t>Nível {0}</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -189,6 +186,9 @@
     <t>Parabéns ao jogador {0} por passar ({1}) e reclamar {2}.</t>
   </si>
   <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
     <t>Enteraccountnumber</t>
   </si>
   <si>
@@ -249,6 +249,15 @@
     <t>Requisitos completos para retirar dinheiro.</t>
   </si>
   <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
@@ -291,6 +300,12 @@
     <t>Informações de pagamento salvas com sucesso</t>
   </si>
   <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.leveltxt</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
@@ -300,10 +315,13 @@
     <t>makeupInfoHint1</t>
   </si>
   <si>
-    <t/>
+    <t>makeupInfoHint2</t>
   </si>
   <si>
-    <t>makeupInfoHint2</t>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
   </si>
   <si>
     <t>MakeUpStep1</t>
@@ -318,13 +336,37 @@
     <t>Colete outro {0} para retirar</t>
   </si>
   <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
     <t>MakeupUIForm.title</t>
   </si>
   <si>
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.txtLevel</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.privacy</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.quit</t>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -459,7 +501,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -483,7 +525,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
@@ -519,11 +561,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
@@ -543,18 +585,82 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -7609,6 +7715,1650 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -7625,1469 +9375,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1073">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1074">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1075">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1076">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1077">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1078">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1079">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1080">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1081">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1082">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1083">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1084">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1085">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1086">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1087">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1088">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1089">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1090">
+            <xdr:cNvPr hidden="1" name="A1" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1090"/>
@@ -9162,18 +9450,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1091">
+            <xdr:cNvPr hidden="1" name="A2" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1091"/>
@@ -9248,18 +9536,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1092">
+            <xdr:cNvPr hidden="1" name="A3" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9334,18 +9622,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1093">
+            <xdr:cNvPr hidden="1" name="A4" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9420,18 +9708,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1094">
+            <xdr:cNvPr hidden="1" name="A5" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9506,18 +9794,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1095">
+            <xdr:cNvPr hidden="1" name="A6" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9592,18 +9880,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1096">
+            <xdr:cNvPr hidden="1" name="A7" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9678,18 +9966,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1097">
+            <xdr:cNvPr hidden="1" name="A8" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -9764,18 +10052,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1098">
+            <xdr:cNvPr hidden="1" name="A9" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -9850,18 +10138,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1099">
+            <xdr:cNvPr hidden="1" name="A10" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -9936,18 +10224,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1100">
+            <xdr:cNvPr hidden="1" name="A11" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -10022,18 +10310,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1101">
+            <xdr:cNvPr hidden="1" name="A12" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -10108,18 +10396,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1102">
+            <xdr:cNvPr hidden="1" name="A13" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10194,18 +10482,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1103">
+            <xdr:cNvPr hidden="1" name="A14" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10280,18 +10568,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1104">
+            <xdr:cNvPr hidden="1" name="A15" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10366,18 +10654,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1105">
+            <xdr:cNvPr hidden="1" name="A16" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10452,18 +10740,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1106">
+            <xdr:cNvPr hidden="1" name="A17" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10538,18 +10826,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1107">
+            <xdr:cNvPr hidden="1" name="A18" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10624,18 +10912,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1108">
+            <xdr:cNvPr hidden="1" name="A19" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10710,18 +10998,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1109">
+            <xdr:cNvPr hidden="1" name="A20" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -10796,18 +11084,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1110">
+            <xdr:cNvPr hidden="1" name="A21" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -10882,18 +11170,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1111">
+            <xdr:cNvPr hidden="1" name="A22" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -10968,18 +11256,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1112">
+            <xdr:cNvPr hidden="1" name="A23" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -11054,18 +11342,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1113">
+            <xdr:cNvPr hidden="1" name="A24" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11140,18 +11428,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1114">
+            <xdr:cNvPr hidden="1" name="A25" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11226,18 +11514,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1115">
+            <xdr:cNvPr hidden="1" name="A26" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11312,18 +11600,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1116">
+            <xdr:cNvPr hidden="1" name="A27" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11398,18 +11686,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1117">
+            <xdr:cNvPr hidden="1" name="A28" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11484,18 +11772,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1118">
+            <xdr:cNvPr hidden="1" name="A29" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -11570,18 +11858,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1119">
+            <xdr:cNvPr hidden="1" name="A30" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -11656,18 +11944,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1120">
+            <xdr:cNvPr hidden="1" name="A31" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1120"/>
@@ -11742,18 +12030,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1121">
+            <xdr:cNvPr hidden="1" name="A32" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1121"/>
@@ -11822,12 +12110,2850 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>32</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A33" id="1122">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1122"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>33</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A34" id="1123">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1123"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>34</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A35" id="1124">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1124"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>35</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A36" id="1125">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1125"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>36</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A37" id="1126">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1126"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>37</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A38" id="1127">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1127"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>38</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A39" id="1128">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1128"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>39</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A40" id="1129">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1129"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>40</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A41" id="1130">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1130"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>41</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A42" id="1131">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1131"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>42</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A43" id="1132">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1132"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>43</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A44" id="1133">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1133"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>44</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A45" id="1134">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1134"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A46" id="1135">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1135"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A47" id="1136">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1136"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>47</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A48" id="1137">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1137"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A49" id="1138">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1138"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A50" id="1139">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1139"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A51" id="1140">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1140"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A52" id="1141">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1141"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A53" id="1142">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1142"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A54" id="1143">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1143"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A55" id="1144">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1144"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A56" id="1145">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1145"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A57" id="1146">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1146"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A58" id="1147">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1147"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A59" id="1148">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1148"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A60" id="1149">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1149"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A61" id="1150">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1150"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A62" id="1151">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1151"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A63" id="1152">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1152"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1153">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1153"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A65" id="1154">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1154"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -11850,430 +14976,574 @@
         <v>2</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
       <c r="B4" s="0" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1"/>
       <c r="B36" s="0" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1"/>
       <c r="B37" s="0" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1"/>
       <c r="B38" s="0" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1"/>
       <c r="B46" s="0" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1"/>
       <c r="B47" s="0" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>81</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1"/>
+      <c r="B50" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1"/>
+      <c r="B51" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1"/>
+      <c r="B52" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="0" t="s">
-        <v>81</v>
+    </row>
+    <row r="53">
+      <c r="A53" s="1"/>
+      <c r="B53" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1"/>
+      <c r="B54" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1"/>
+      <c r="B55" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1"/>
+      <c r="B56" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1"/>
+      <c r="B57" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1"/>
+      <c r="B58" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1"/>
+      <c r="B59" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1"/>
+      <c r="B60" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1"/>
+      <c r="B61" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1"/>
+      <c r="B62" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1"/>
+      <c r="B63" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1"/>
+      <c r="B64" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1"/>
+      <c r="B65" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -12285,7 +15555,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId1732" name="A1">
+            <control shapeId="1090" r:id="rId2136" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12307,7 +15577,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId1733" name="A2">
+            <control shapeId="1091" r:id="rId2137" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12329,7 +15599,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId1734" name="A3">
+            <control shapeId="1092" r:id="rId2138" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12351,7 +15621,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId1735" name="A4">
+            <control shapeId="1093" r:id="rId2139" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12373,7 +15643,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId1736" name="A5">
+            <control shapeId="1094" r:id="rId2140" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12395,7 +15665,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId1737" name="A6">
+            <control shapeId="1095" r:id="rId2141" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12417,7 +15687,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId1738" name="A7">
+            <control shapeId="1096" r:id="rId2142" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12439,7 +15709,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId1739" name="A8">
+            <control shapeId="1097" r:id="rId2143" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12461,7 +15731,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId1740" name="A9">
+            <control shapeId="1098" r:id="rId2144" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12483,7 +15753,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId1741" name="A10">
+            <control shapeId="1099" r:id="rId2145" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12505,7 +15775,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId1742" name="A11">
+            <control shapeId="1100" r:id="rId2146" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12527,7 +15797,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId1743" name="A12">
+            <control shapeId="1101" r:id="rId2147" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12549,7 +15819,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId1744" name="A13">
+            <control shapeId="1102" r:id="rId2148" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12571,7 +15841,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId1745" name="A14">
+            <control shapeId="1103" r:id="rId2149" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12593,7 +15863,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId1746" name="A15">
+            <control shapeId="1104" r:id="rId2150" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12615,7 +15885,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId1747" name="A16">
+            <control shapeId="1105" r:id="rId2151" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12637,7 +15907,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId1748" name="A17">
+            <control shapeId="1106" r:id="rId2152" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12659,7 +15929,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId1749" name="A18">
+            <control shapeId="1107" r:id="rId2153" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12681,7 +15951,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId1750" name="A19">
+            <control shapeId="1108" r:id="rId2154" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12703,7 +15973,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId1751" name="A20">
+            <control shapeId="1109" r:id="rId2155" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12725,7 +15995,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId1752" name="A21">
+            <control shapeId="1110" r:id="rId2156" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12747,7 +16017,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId1753" name="A22">
+            <control shapeId="1111" r:id="rId2157" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12769,7 +16039,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId1754" name="A23">
+            <control shapeId="1112" r:id="rId2158" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12791,7 +16061,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId1755" name="A24">
+            <control shapeId="1113" r:id="rId2159" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12813,7 +16083,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId1756" name="A25">
+            <control shapeId="1114" r:id="rId2160" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12835,7 +16105,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId1757" name="A26">
+            <control shapeId="1115" r:id="rId2161" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12857,7 +16127,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId1758" name="A27">
+            <control shapeId="1116" r:id="rId2162" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12879,7 +16149,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId1759" name="A28">
+            <control shapeId="1117" r:id="rId2163" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12901,7 +16171,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId1760" name="A29">
+            <control shapeId="1118" r:id="rId2164" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12923,7 +16193,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId1761" name="A30">
+            <control shapeId="1119" r:id="rId2165" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12945,7 +16215,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId1762" name="A31">
+            <control shapeId="1120" r:id="rId2166" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12967,7 +16237,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId1763" name="A32">
+            <control shapeId="1121" r:id="rId2167" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -12989,7 +16259,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId1764" name="A33">
+            <control shapeId="1122" r:id="rId2168" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13011,7 +16281,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId1765" name="A34">
+            <control shapeId="1123" r:id="rId2169" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13033,7 +16303,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId1766" name="A35">
+            <control shapeId="1124" r:id="rId2170" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13055,7 +16325,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId1767" name="A36">
+            <control shapeId="1125" r:id="rId2171" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13077,7 +16347,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId1768" name="A37">
+            <control shapeId="1126" r:id="rId2172" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13099,7 +16369,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId1769" name="A38">
+            <control shapeId="1127" r:id="rId2173" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13121,7 +16391,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId1770" name="A39">
+            <control shapeId="1128" r:id="rId2174" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13143,7 +16413,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId1771" name="A40">
+            <control shapeId="1129" r:id="rId2175" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13165,7 +16435,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId1772" name="A41">
+            <control shapeId="1130" r:id="rId2176" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13187,7 +16457,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId1773" name="A42">
+            <control shapeId="1131" r:id="rId2177" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13209,7 +16479,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId1774" name="A43">
+            <control shapeId="1132" r:id="rId2178" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13231,7 +16501,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId1775" name="A44">
+            <control shapeId="1133" r:id="rId2179" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13253,7 +16523,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId1776" name="A45">
+            <control shapeId="1134" r:id="rId2180" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13275,7 +16545,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId1777" name="A46">
+            <control shapeId="1135" r:id="rId2181" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13297,7 +16567,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId1778" name="A47">
+            <control shapeId="1136" r:id="rId2182" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13319,7 +16589,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId1779" name="A48">
+            <control shapeId="1137" r:id="rId2183" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13341,7 +16611,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId1780" name="A49">
+            <control shapeId="1138" r:id="rId2184" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -13361,6 +16631,358 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1139" r:id="rId2185" name="A50">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1140" r:id="rId2186" name="A51">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1141" r:id="rId2187" name="A52">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1142" r:id="rId2188" name="A53">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1143" r:id="rId2189" name="A54">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1144" r:id="rId2190" name="A55">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1145" r:id="rId2191" name="A56">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1146" r:id="rId2192" name="A57">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1147" r:id="rId2193" name="A58">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1148" r:id="rId2194" name="A59">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1149" r:id="rId2195" name="A60">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1150" r:id="rId2196" name="A61">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1151" r:id="rId2197" name="A62">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1152" r:id="rId2198" name="A63">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1153" r:id="rId2199" name="A64">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1154" r:id="rId2200" name="A65">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -186,6 +186,9 @@
     <t>Parabéns ao jogador {0} por passar ({1}) e reclamar {2}.</t>
   </si>
   <si>
+    <t>claim</t>
+  </si>
+  <si>
     <t>CoinRewardUIForm.titletxt</t>
   </si>
   <si>
@@ -300,10 +303,13 @@
     <t>Informações de pagamento salvas com sucesso</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
-    <t>LevelCompleteUIForm.leveltxt</t>
+    <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
     <t>MakeUpFail</t>
@@ -349,9 +355,6 @@
   </si>
   <si>
     <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
     <t>QuitConfirmUIForm.desc</t>
@@ -509,7 +512,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
@@ -529,7 +532,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -585,11 +588,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,11 +600,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
@@ -664,6 +667,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -678,6 +685,1066 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -9375,179 +10442,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1090">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1091">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1092">
+            <xdr:cNvPr hidden="1" name="A1" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1092"/>
@@ -9622,18 +10517,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1093">
+            <xdr:cNvPr hidden="1" name="A2" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1093"/>
@@ -9708,18 +10603,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1094">
+            <xdr:cNvPr hidden="1" name="A3" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1094"/>
@@ -9794,18 +10689,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1095">
+            <xdr:cNvPr hidden="1" name="A4" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1095"/>
@@ -9880,18 +10775,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1096">
+            <xdr:cNvPr hidden="1" name="A5" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1096"/>
@@ -9966,18 +10861,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1097">
+            <xdr:cNvPr hidden="1" name="A6" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1097"/>
@@ -10052,18 +10947,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1098">
+            <xdr:cNvPr hidden="1" name="A7" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1098"/>
@@ -10138,18 +11033,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1099">
+            <xdr:cNvPr hidden="1" name="A8" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1099"/>
@@ -10224,18 +11119,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1100">
+            <xdr:cNvPr hidden="1" name="A9" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1100"/>
@@ -10310,18 +11205,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1101">
+            <xdr:cNvPr hidden="1" name="A10" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1101"/>
@@ -10396,18 +11291,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1102">
+            <xdr:cNvPr hidden="1" name="A11" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1102"/>
@@ -10482,18 +11377,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1103">
+            <xdr:cNvPr hidden="1" name="A12" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1103"/>
@@ -10568,18 +11463,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1104">
+            <xdr:cNvPr hidden="1" name="A13" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1104"/>
@@ -10654,18 +11549,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1105">
+            <xdr:cNvPr hidden="1" name="A14" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1105"/>
@@ -10740,18 +11635,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1106">
+            <xdr:cNvPr hidden="1" name="A15" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1106"/>
@@ -10826,18 +11721,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1107">
+            <xdr:cNvPr hidden="1" name="A16" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1107"/>
@@ -10912,18 +11807,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1108">
+            <xdr:cNvPr hidden="1" name="A17" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1108"/>
@@ -10998,18 +11893,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1109">
+            <xdr:cNvPr hidden="1" name="A18" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1109"/>
@@ -11084,18 +11979,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1110">
+            <xdr:cNvPr hidden="1" name="A19" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1110"/>
@@ -11170,18 +12065,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1111">
+            <xdr:cNvPr hidden="1" name="A20" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1111"/>
@@ -11256,18 +12151,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1112">
+            <xdr:cNvPr hidden="1" name="A21" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1112"/>
@@ -11342,18 +12237,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
+          <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1113">
+            <xdr:cNvPr hidden="1" name="A22" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1113"/>
@@ -11428,18 +12323,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
+          <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1114">
+            <xdr:cNvPr hidden="1" name="A23" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1114"/>
@@ -11514,18 +12409,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1115">
+            <xdr:cNvPr hidden="1" name="A24" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1115"/>
@@ -11600,18 +12495,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
+          <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1116">
+            <xdr:cNvPr hidden="1" name="A25" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1116"/>
@@ -11686,18 +12581,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
+          <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1117">
+            <xdr:cNvPr hidden="1" name="A26" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1117"/>
@@ -11772,18 +12667,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
+          <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1118">
+            <xdr:cNvPr hidden="1" name="A27" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1118"/>
@@ -11858,18 +12753,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1119">
+            <xdr:cNvPr hidden="1" name="A28" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1119"/>
@@ -11944,18 +12839,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
+          <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1120">
+            <xdr:cNvPr hidden="1" name="A29" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1120"/>
@@ -12030,18 +12925,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>31</xdr:row>
+          <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1121">
+            <xdr:cNvPr hidden="1" name="A30" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1121"/>
@@ -12116,18 +13011,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>32</xdr:row>
+          <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1122">
+            <xdr:cNvPr hidden="1" name="A31" id="1122">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1122"/>
@@ -12202,18 +13097,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>33</xdr:row>
+          <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1123">
+            <xdr:cNvPr hidden="1" name="A32" id="1123">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1123"/>
@@ -12288,18 +13183,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>34</xdr:row>
+          <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1124">
+            <xdr:cNvPr hidden="1" name="A33" id="1124">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1124"/>
@@ -12374,18 +13269,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>35</xdr:row>
+          <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1125">
+            <xdr:cNvPr hidden="1" name="A34" id="1125">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1125"/>
@@ -12460,18 +13355,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>36</xdr:row>
+          <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1126">
+            <xdr:cNvPr hidden="1" name="A35" id="1126">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1126"/>
@@ -12546,18 +13441,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>37</xdr:row>
+          <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1127">
+            <xdr:cNvPr hidden="1" name="A36" id="1127">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1127"/>
@@ -12632,18 +13527,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>38</xdr:row>
+          <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1128">
+            <xdr:cNvPr hidden="1" name="A37" id="1128">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1128"/>
@@ -12718,18 +13613,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>39</xdr:row>
+          <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1129">
+            <xdr:cNvPr hidden="1" name="A38" id="1129">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1129"/>
@@ -12804,18 +13699,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>40</xdr:row>
+          <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1130">
+            <xdr:cNvPr hidden="1" name="A39" id="1130">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1130"/>
@@ -12890,18 +13785,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>41</xdr:row>
+          <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1131">
+            <xdr:cNvPr hidden="1" name="A40" id="1131">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1131"/>
@@ -12976,18 +13871,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>42</xdr:row>
+          <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1132">
+            <xdr:cNvPr hidden="1" name="A41" id="1132">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1132"/>
@@ -13062,18 +13957,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>43</xdr:row>
+          <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1133">
+            <xdr:cNvPr hidden="1" name="A42" id="1133">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1133"/>
@@ -13148,18 +14043,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>44</xdr:row>
+          <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1134">
+            <xdr:cNvPr hidden="1" name="A43" id="1134">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1134"/>
@@ -13234,18 +14129,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>45</xdr:row>
+          <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1135">
+            <xdr:cNvPr hidden="1" name="A44" id="1135">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1135"/>
@@ -13320,18 +14215,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>46</xdr:row>
+          <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1136">
+            <xdr:cNvPr hidden="1" name="A45" id="1136">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1136"/>
@@ -13406,18 +14301,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>47</xdr:row>
+          <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1137">
+            <xdr:cNvPr hidden="1" name="A46" id="1137">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1137"/>
@@ -13492,18 +14387,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>48</xdr:row>
+          <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1138">
+            <xdr:cNvPr hidden="1" name="A47" id="1138">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1138"/>
@@ -13578,18 +14473,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>49</xdr:row>
+          <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1139">
+            <xdr:cNvPr hidden="1" name="A48" id="1139">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1139"/>
@@ -13664,18 +14559,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>50</xdr:row>
+          <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1140">
+            <xdr:cNvPr hidden="1" name="A49" id="1140">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1140"/>
@@ -13750,18 +14645,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>51</xdr:row>
+          <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1141">
+            <xdr:cNvPr hidden="1" name="A50" id="1141">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1141"/>
@@ -13836,18 +14731,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>52</xdr:row>
+          <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1142">
+            <xdr:cNvPr hidden="1" name="A51" id="1142">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1142"/>
@@ -13922,18 +14817,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>53</xdr:row>
+          <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1143">
+            <xdr:cNvPr hidden="1" name="A52" id="1143">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1143"/>
@@ -14008,18 +14903,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>54</xdr:row>
+          <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1144">
+            <xdr:cNvPr hidden="1" name="A53" id="1144">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1144"/>
@@ -14094,18 +14989,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>55</xdr:row>
+          <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1145">
+            <xdr:cNvPr hidden="1" name="A54" id="1145">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1145"/>
@@ -14180,18 +15075,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>56</xdr:row>
+          <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1146">
+            <xdr:cNvPr hidden="1" name="A55" id="1146">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1146"/>
@@ -14266,18 +15161,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>57</xdr:row>
+          <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1147">
+            <xdr:cNvPr hidden="1" name="A56" id="1147">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1147"/>
@@ -14352,18 +15247,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>58</xdr:row>
+          <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1148">
+            <xdr:cNvPr hidden="1" name="A57" id="1148">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1148"/>
@@ -14438,18 +15333,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>59</xdr:row>
+          <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1149">
+            <xdr:cNvPr hidden="1" name="A58" id="1149">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1149"/>
@@ -14524,18 +15419,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>60</xdr:row>
+          <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1150">
+            <xdr:cNvPr hidden="1" name="A59" id="1150">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1150"/>
@@ -14610,18 +15505,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>61</xdr:row>
+          <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1151">
+            <xdr:cNvPr hidden="1" name="A60" id="1151">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1151"/>
@@ -14696,18 +15591,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>62</xdr:row>
+          <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1152">
+            <xdr:cNvPr hidden="1" name="A61" id="1152">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1152"/>
@@ -14782,18 +15677,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>63</xdr:row>
+          <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1153">
+            <xdr:cNvPr hidden="1" name="A62" id="1153">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1153"/>
@@ -14868,18 +15763,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>64</xdr:row>
+          <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>65</xdr:row>
+          <xdr:row>63</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1154">
+            <xdr:cNvPr hidden="1" name="A63" id="1154">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1154"/>
@@ -14948,12 +15843,270 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1155">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1155"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A65" id="1156">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1156"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A66" id="1157">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1157"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -15183,97 +16336,97 @@
         <v>44</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1"/>
       <c r="B32" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1"/>
       <c r="B33" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1"/>
       <c r="B34" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1"/>
       <c r="B35" s="0" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36">
@@ -15300,70 +16453,70 @@
         <v>67</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1"/>
       <c r="B39" s="0" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1"/>
       <c r="B40" s="0" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1"/>
       <c r="B41" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1"/>
       <c r="B42" s="0" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1"/>
       <c r="B43" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1"/>
       <c r="B44" s="0" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1"/>
       <c r="B45" s="0" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
@@ -15381,13 +16534,13 @@
         <v>83</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1"/>
       <c r="B48" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>1</v>
@@ -15396,10 +16549,10 @@
     <row r="49">
       <c r="A49" s="1"/>
       <c r="B49" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -15426,34 +16579,34 @@
         <v>89</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1"/>
       <c r="B53" s="0" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1"/>
       <c r="B54" s="0" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1"/>
       <c r="B55" s="0" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56">
@@ -15546,6 +16699,15 @@
         <v>1</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="1"/>
+      <c r="B66" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -15555,7 +16717,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId2136" name="A1">
+            <control shapeId="1092" r:id="rId2397" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15577,7 +16739,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId2137" name="A2">
+            <control shapeId="1093" r:id="rId2398" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15599,7 +16761,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId2138" name="A3">
+            <control shapeId="1094" r:id="rId2399" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15621,7 +16783,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId2139" name="A4">
+            <control shapeId="1095" r:id="rId2400" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15643,7 +16805,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId2140" name="A5">
+            <control shapeId="1096" r:id="rId2401" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15665,7 +16827,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId2141" name="A6">
+            <control shapeId="1097" r:id="rId2402" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15687,7 +16849,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId2142" name="A7">
+            <control shapeId="1098" r:id="rId2403" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15709,7 +16871,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId2143" name="A8">
+            <control shapeId="1099" r:id="rId2404" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15731,7 +16893,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId2144" name="A9">
+            <control shapeId="1100" r:id="rId2405" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15753,7 +16915,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId2145" name="A10">
+            <control shapeId="1101" r:id="rId2406" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15775,7 +16937,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId2146" name="A11">
+            <control shapeId="1102" r:id="rId2407" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15797,7 +16959,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId2147" name="A12">
+            <control shapeId="1103" r:id="rId2408" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15819,7 +16981,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId2148" name="A13">
+            <control shapeId="1104" r:id="rId2409" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15841,7 +17003,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId2149" name="A14">
+            <control shapeId="1105" r:id="rId2410" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15863,7 +17025,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId2150" name="A15">
+            <control shapeId="1106" r:id="rId2411" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15885,7 +17047,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId2151" name="A16">
+            <control shapeId="1107" r:id="rId2412" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15907,7 +17069,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId2152" name="A17">
+            <control shapeId="1108" r:id="rId2413" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15929,7 +17091,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId2153" name="A18">
+            <control shapeId="1109" r:id="rId2414" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15951,7 +17113,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId2154" name="A19">
+            <control shapeId="1110" r:id="rId2415" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15973,7 +17135,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId2155" name="A20">
+            <control shapeId="1111" r:id="rId2416" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -15995,7 +17157,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId2156" name="A21">
+            <control shapeId="1112" r:id="rId2417" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16017,7 +17179,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId2157" name="A22">
+            <control shapeId="1113" r:id="rId2418" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16039,7 +17201,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId2158" name="A23">
+            <control shapeId="1114" r:id="rId2419" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16061,7 +17223,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId2159" name="A24">
+            <control shapeId="1115" r:id="rId2420" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16083,7 +17245,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId2160" name="A25">
+            <control shapeId="1116" r:id="rId2421" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16105,7 +17267,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId2161" name="A26">
+            <control shapeId="1117" r:id="rId2422" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16127,7 +17289,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId2162" name="A27">
+            <control shapeId="1118" r:id="rId2423" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16149,7 +17311,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId2163" name="A28">
+            <control shapeId="1119" r:id="rId2424" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16171,7 +17333,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId2164" name="A29">
+            <control shapeId="1120" r:id="rId2425" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16193,7 +17355,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId2165" name="A30">
+            <control shapeId="1121" r:id="rId2426" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16215,7 +17377,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId2166" name="A31">
+            <control shapeId="1122" r:id="rId2427" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16237,7 +17399,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId2167" name="A32">
+            <control shapeId="1123" r:id="rId2428" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16259,7 +17421,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId2168" name="A33">
+            <control shapeId="1124" r:id="rId2429" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16281,7 +17443,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId2169" name="A34">
+            <control shapeId="1125" r:id="rId2430" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16303,7 +17465,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId2170" name="A35">
+            <control shapeId="1126" r:id="rId2431" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16325,7 +17487,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId2171" name="A36">
+            <control shapeId="1127" r:id="rId2432" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16347,7 +17509,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId2172" name="A37">
+            <control shapeId="1128" r:id="rId2433" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16369,7 +17531,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId2173" name="A38">
+            <control shapeId="1129" r:id="rId2434" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16391,7 +17553,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId2174" name="A39">
+            <control shapeId="1130" r:id="rId2435" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16413,7 +17575,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId2175" name="A40">
+            <control shapeId="1131" r:id="rId2436" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16435,7 +17597,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId2176" name="A41">
+            <control shapeId="1132" r:id="rId2437" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16457,7 +17619,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId2177" name="A42">
+            <control shapeId="1133" r:id="rId2438" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16479,7 +17641,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId2178" name="A43">
+            <control shapeId="1134" r:id="rId2439" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16501,7 +17663,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId2179" name="A44">
+            <control shapeId="1135" r:id="rId2440" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16523,7 +17685,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId2180" name="A45">
+            <control shapeId="1136" r:id="rId2441" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16545,7 +17707,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId2181" name="A46">
+            <control shapeId="1137" r:id="rId2442" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16567,7 +17729,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId2182" name="A47">
+            <control shapeId="1138" r:id="rId2443" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16589,7 +17751,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId2183" name="A48">
+            <control shapeId="1139" r:id="rId2444" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16611,7 +17773,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId2184" name="A49">
+            <control shapeId="1140" r:id="rId2445" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16633,7 +17795,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId2185" name="A50">
+            <control shapeId="1141" r:id="rId2446" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16655,7 +17817,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId2186" name="A51">
+            <control shapeId="1142" r:id="rId2447" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16677,7 +17839,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId2187" name="A52">
+            <control shapeId="1143" r:id="rId2448" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16699,7 +17861,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId2188" name="A53">
+            <control shapeId="1144" r:id="rId2449" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16721,7 +17883,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId2189" name="A54">
+            <control shapeId="1145" r:id="rId2450" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16743,7 +17905,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId2190" name="A55">
+            <control shapeId="1146" r:id="rId2451" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16765,7 +17927,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId2191" name="A56">
+            <control shapeId="1147" r:id="rId2452" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16787,7 +17949,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId2192" name="A57">
+            <control shapeId="1148" r:id="rId2453" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16809,7 +17971,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId2193" name="A58">
+            <control shapeId="1149" r:id="rId2454" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16831,7 +17993,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId2194" name="A59">
+            <control shapeId="1150" r:id="rId2455" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16853,7 +18015,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId2195" name="A60">
+            <control shapeId="1151" r:id="rId2456" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16875,7 +18037,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId2196" name="A61">
+            <control shapeId="1152" r:id="rId2457" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16897,7 +18059,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId2197" name="A62">
+            <control shapeId="1153" r:id="rId2458" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16919,7 +18081,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId2198" name="A63">
+            <control shapeId="1154" r:id="rId2459" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16941,7 +18103,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId2199" name="A64">
+            <control shapeId="1155" r:id="rId2460" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16963,7 +18125,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId2200" name="A65">
+            <control shapeId="1156" r:id="rId2461" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -16983,6 +18145,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1157" r:id="rId2462" name="A66">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -140,6 +140,9 @@
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
+    <t>Sacar</t>
+  </si>
+  <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
@@ -338,9 +341,6 @@
     <t>MakeupUIForm.title</t>
   </si>
   <si>
-    <t>Sacar</t>
-  </si>
-  <si>
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>Vença {0} fases!</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm.title</t>
   </si>
 </sst>
 </file>
@@ -677,6 +680,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6367,12 +6374,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A67" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6554,20 +6647,20 @@
         <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>13</v>
@@ -6575,7 +6668,7 @@
     </row>
     <row r="25">
       <c r="B25" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>23</v>
@@ -6583,87 +6676,87 @@
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -6671,7 +6764,7 @@
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>38</v>
@@ -6679,170 +6772,170 @@
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>108</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59">
@@ -6907,6 +7000,14 @@
       </c>
       <c r="C66" s="1" t="s">
         <v>122</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8368,6 +8469,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1091" r:id="rId69" name="A67">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -278,6 +278,9 @@
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
+    <t>Concluído</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -384,6 +387,69 @@
   </si>
   <si>
     <t>MakeupRecordUIForm.title</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>Vidas extras</t>
+  </si>
+  <si>
+    <t>AddPropUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>Foguete</t>
+  </si>
+  <si>
+    <t>PlayLoadingUIForm.loading</t>
+  </si>
+  <si>
+    <t>Carregando...</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quit</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.avatarTxt</t>
+  </si>
+  <si>
+    <t>Selecione um avatar:</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterDesc</t>
+  </si>
+  <si>
+    <t>Digite sua conta do PayPal</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterAgainDesc</t>
+  </si>
+  <si>
+    <t>Digite a conta do PayPal novamente</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.confirm</t>
+  </si>
+  <si>
+    <t>Confirmar</t>
+  </si>
+  <si>
+    <t>TaskItem.adTxt</t>
+  </si>
+  <si>
+    <t>Assista a um anúncio!</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>Grátis</t>
+  </si>
+  <si>
+    <t>TaskItem.go</t>
+  </si>
+  <si>
+    <t>Ir</t>
   </si>
 </sst>
 </file>
@@ -684,7 +750,51 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6460,12 +6570,958 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A68" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A70" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A71" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A72" id="1096">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A73" id="1097">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A74" id="1098">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1098"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A75" id="1099">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1099"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A76" id="1100">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1100"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A77" id="1101">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1101"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A78" id="1102">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1102"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6847,92 +7903,92 @@
         <v>87</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>42</v>
@@ -6940,39 +7996,39 @@
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -6980,7 +8036,7 @@
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -6988,26 +8044,114 @@
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -8491,6 +9635,248 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1092" r:id="rId70" name="A68">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId72" name="A70">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId73" name="A71">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1096" r:id="rId74" name="A72">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1097" r:id="rId75" name="A73">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1098" r:id="rId76" name="A74">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1099" r:id="rId77" name="A75">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1100" r:id="rId78" name="A76">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1101" r:id="rId79" name="A77">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1102" r:id="rId80" name="A78">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -450,6 +450,15 @@
   </si>
   <si>
     <t>Ir</t>
+  </si>
+  <si>
+    <t>cashoutHint</t>
+  </si>
+  <si>
+    <t>Você precisa concluir {0} fases e acumular um saldo de {1} para poder resgatar.</t>
+  </si>
+  <si>
+    <t>MakeupItem.cashout</t>
   </si>
 </sst>
 </file>
@@ -798,7 +807,15 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -7516,12 +7533,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A79" id="1103">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1103"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A80" id="1104">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1104"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8152,6 +8341,22 @@
       </c>
       <c r="C78" s="1" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -9877,6 +10082,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1103" r:id="rId81" name="A79">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1104" r:id="rId82" name="A80">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -188,7 +188,7 @@
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>Toque para mover</t>
+    <t>Toque nesse objeto e dispare o canhão!</t>
   </si>
   <si>
     <t>GuidTxt3</t>
@@ -459,6 +459,42 @@
   </si>
   <si>
     <t>MakeupItem.cashout</t>
+  </si>
+  <si>
+    <t>GuidTxt2</t>
+  </si>
+  <si>
+    <t>Elimine todos os objetos antes que os disparos acabem!</t>
+  </si>
+  <si>
+    <t>MakeupRecordItem.bouns</t>
+  </si>
+  <si>
+    <t>Prêmio total de hoje</t>
+  </si>
+  <si>
+    <t>PlayUIForm.txtHint</t>
+  </si>
+  <si>
+    <t>Toque nos objetos sobre a mesa</t>
+  </si>
+  <si>
+    <t>MakeupItem.reach</t>
+  </si>
+  <si>
+    <t>Saldo necessário</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.desc</t>
+  </si>
+  <si>
+    <t>Selecione um reforço:</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm.desc</t>
+  </si>
+  <si>
+    <t>Agradecemos sua generosa doação!</t>
   </si>
 </sst>
 </file>
@@ -604,19 +640,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,6 +855,30 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7705,12 +7765,528 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A81" id="1105">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1105"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A82" id="1106">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1106"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A83" id="1107">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1107"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A84" id="1108">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1108"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A85" id="1109">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1109"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>86</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A86" id="1110">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1110"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8357,6 +8933,54 @@
       </c>
       <c r="C80" s="1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -10126,6 +10750,138 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1105" r:id="rId83" name="A81">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1106" r:id="rId84" name="A82">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1107" r:id="rId85" name="A83">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1108" r:id="rId86" name="A84">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1109" r:id="rId87" name="A85">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1110" r:id="rId88" name="A86">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>86</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -26,24 +26,6 @@
     <t>Continuar?</t>
   </si>
   <si>
-    <t>ArrowMazeOverUIForm.GameOver</t>
-  </si>
-  <si>
-    <t>Desafio de vitórias consecutivas fracassado</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.restart</t>
-  </si>
-  <si>
-    <t>Reiniciar</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.Revive</t>
-  </si>
-  <si>
-    <t>Reviver</t>
-  </si>
-  <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
@@ -56,319 +38,241 @@
     <t>Resgatar</t>
   </si>
   <si>
-    <t>ArrowRewardDialogUIForm.Continue</t>
+    <t>ArrowRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Parabéns</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.OFF</t>
+  </si>
+  <si>
+    <t>desativado</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.ON</t>
+  </si>
+  <si>
+    <t>ativado</t>
+  </si>
+  <si>
+    <t>ArrowUITopbar.cashOut</t>
+  </si>
+  <si>
+    <t>Sacar</t>
+  </si>
+  <si>
+    <t>ArrowWithdrawalInfoItem.infoTxt</t>
+  </si>
+  <si>
+    <t>Parabéns ao jogador {0} por concluir ({1}) e resgatar {2}.</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Enteraccountnumber</t>
+  </si>
+  <si>
+    <t>Digite sua conta</t>
+  </si>
+  <si>
+    <t>EnterCPF</t>
+  </si>
+  <si>
+    <t>Digite o CPF</t>
+  </si>
+  <si>
+    <t>Enteremail</t>
+  </si>
+  <si>
+    <t>Confirme o e-mail</t>
+  </si>
+  <si>
+    <t>EnterFullName</t>
+  </si>
+  <si>
+    <t>Digite o nome completo</t>
+  </si>
+  <si>
+    <t>EnterPayPalaccount</t>
+  </si>
+  <si>
+    <t>Digite a conta do PayPal</t>
+  </si>
+  <si>
+    <t>GuidTxt1</t>
+  </si>
+  <si>
+    <t>Toque nesse objeto e dispare o canhão!</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>Início</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>Configurações</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>Tarefa</t>
+  </si>
+  <si>
+    <t>InfoErrTips1</t>
+  </si>
+  <si>
+    <t>Digite um endereço de e-mail válido</t>
+  </si>
+  <si>
+    <t>InfoErrTips2</t>
+  </si>
+  <si>
+    <t>Digite um CPF válido</t>
+  </si>
+  <si>
+    <t>InfoErrTips3</t>
+  </si>
+  <si>
+    <t>A conta do PayPal deve ser um e-mail válido</t>
+  </si>
+  <si>
+    <t>InfoErrTips4</t>
+  </si>
+  <si>
+    <t>Digite seu nome completo</t>
+  </si>
+  <si>
+    <t>InfoErrTips5</t>
+  </si>
+  <si>
+    <t>Digite o número da sua conta</t>
+  </si>
+  <si>
+    <t>InfoErrTips6</t>
+  </si>
+  <si>
+    <t>Selecione uma forma de pagamento</t>
+  </si>
+  <si>
+    <t>InfoErrTips7</t>
+  </si>
+  <si>
+    <t>Dados de pagamento salvos com sucesso</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>Fase {0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>Concluído</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.next</t>
+  </si>
+  <si>
+    <t>Próximo</t>
+  </si>
+  <si>
+    <t>MakeUpFail</t>
+  </si>
+  <si>
+    <t>Infelizmente, o resgate falhou.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t>Verifique se a conta do PayPal foi digitada da mesma forma nos dois campos.</t>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
+    <t>Digite o e-mail no formato correto.</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>Saque em andamento</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Forma de pagamento</t>
+  </si>
+  <si>
+    <t>MakeUpStep1</t>
+  </si>
+  <si>
+    <t>Conclua a fase {0} para sacar</t>
+  </si>
+  <si>
+    <t>MakeUpStep2</t>
+  </si>
+  <si>
+    <t>Colete mais {0} para sacar</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>Inserir</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
+    <t>Histórico</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
+    <t>Saldo {0}=$1</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
+    <t>Assista a anúncios para obter itens do jogo no baú.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>Se sair agora, perderá uma vida.</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>Sair?</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>Continuar</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.NextLevel</t>
-  </si>
-  <si>
-    <t>Próxima fase</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Recompensas de combo</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.winTitle</t>
-  </si>
-  <si>
-    <t>FASE CONCLUÍDA</t>
-  </si>
-  <si>
-    <t>ArrowRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Parabéns</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.OFF</t>
-  </si>
-  <si>
-    <t>desativado</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.ON</t>
-  </si>
-  <si>
-    <t>ativado</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Home</t>
-  </si>
-  <si>
-    <t>Início</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Music</t>
-  </si>
-  <si>
-    <t>Música</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Privacy</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Resume</t>
-  </si>
-  <si>
-    <t>Retomar</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Sound</t>
-  </si>
-  <si>
-    <t>Som</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Text_Title</t>
-  </si>
-  <si>
-    <t>Configurações</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Vibrate</t>
-  </si>
-  <si>
-    <t>Vibração</t>
-  </si>
-  <si>
-    <t>ArrowUITopbar.cashOut</t>
-  </si>
-  <si>
-    <t>Sacar</t>
-  </si>
-  <si>
-    <t>ArrowWithdrawalInfoItem.infoTxt</t>
-  </si>
-  <si>
-    <t>Parabéns ao jogador {0} por concluir ({1}) e resgatar {2}.</t>
-  </si>
-  <si>
-    <t>claim</t>
-  </si>
-  <si>
-    <t>CoinRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Enteraccountnumber</t>
-  </si>
-  <si>
-    <t>Digite sua conta</t>
-  </si>
-  <si>
-    <t>EnterCPF</t>
-  </si>
-  <si>
-    <t>Digite o CPF</t>
-  </si>
-  <si>
-    <t>Enteremail</t>
-  </si>
-  <si>
-    <t>Confirme o e-mail</t>
-  </si>
-  <si>
-    <t>EnterFullName</t>
-  </si>
-  <si>
-    <t>Digite o nome completo</t>
-  </si>
-  <si>
-    <t>EnterPayPalaccount</t>
-  </si>
-  <si>
-    <t>Digite a conta do PayPal</t>
-  </si>
-  <si>
-    <t>GuidTxt1</t>
-  </si>
-  <si>
-    <t>Toque nesse objeto e dispare o canhão!</t>
-  </si>
-  <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toque aqui para sacar </t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>Afaste os dedos para ampliar</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confira seu saldo atual aqui. </t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
-  </si>
-  <si>
-    <t>Cumpra os requisitos para sacar.</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.home</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.setting</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.task</t>
-  </si>
-  <si>
-    <t>Tarefa</t>
-  </si>
-  <si>
-    <t>InfoErrTips1</t>
-  </si>
-  <si>
-    <t>Digite um endereço de e-mail válido</t>
-  </si>
-  <si>
-    <t>InfoErrTips2</t>
-  </si>
-  <si>
-    <t>Digite um CPF válido</t>
-  </si>
-  <si>
-    <t>InfoErrTips3</t>
-  </si>
-  <si>
-    <t>A conta do PayPal deve ser um e-mail válido</t>
-  </si>
-  <si>
-    <t>InfoErrTips4</t>
-  </si>
-  <si>
-    <t>Digite seu nome completo</t>
-  </si>
-  <si>
-    <t>InfoErrTips5</t>
-  </si>
-  <si>
-    <t>Digite o número da sua conta</t>
-  </si>
-  <si>
-    <t>InfoErrTips6</t>
-  </si>
-  <si>
-    <t>Selecione uma forma de pagamento</t>
-  </si>
-  <si>
-    <t>InfoErrTips7</t>
-  </si>
-  <si>
-    <t>Dados de pagamento salvos com sucesso</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Fase {0}</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.complete</t>
-  </si>
-  <si>
-    <t>Concluído</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.next</t>
-  </si>
-  <si>
-    <t>Próximo</t>
-  </si>
-  <si>
-    <t>MakeUpFail</t>
-  </si>
-  <si>
-    <t>Infelizmente, o resgate falhou.</t>
-  </si>
-  <si>
-    <t>makeupInfoHint1</t>
-  </si>
-  <si>
-    <t>Verifique se a conta do PayPal foi digitada da mesma forma nos dois campos.</t>
-  </si>
-  <si>
-    <t>makeupInfoHint2</t>
-  </si>
-  <si>
-    <t>Digite o e-mail no formato correto.</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>Saque em andamento</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Forma de pagamento</t>
-  </si>
-  <si>
-    <t>MakeUpStep1</t>
-  </si>
-  <si>
-    <t>Conclua a fase {0} para sacar</t>
-  </si>
-  <si>
-    <t>MakeUpStep2</t>
-  </si>
-  <si>
-    <t>Colete mais {0} para sacar</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.input</t>
-  </si>
-  <si>
-    <t>Inserir</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.record</t>
-  </si>
-  <si>
-    <t>Histórico</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.title</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.txtBalance</t>
-  </si>
-  <si>
-    <t>Saldo {0}=$1</t>
-  </si>
-  <si>
-    <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>Assista a anúncios para obter itens do jogo no baú.</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.desc</t>
-  </si>
-  <si>
-    <t>Se sair agora, perderá uma vida.</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.quitTxt</t>
-  </si>
-  <si>
-    <t>Sair?</t>
-  </si>
-  <si>
-    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>SettingPageUIForm.privacy</t>
@@ -552,27 +456,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -592,23 +496,23 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -624,7 +528,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -632,7 +536,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
@@ -640,11 +544,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,11 +560,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,7 +572,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -676,31 +580,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
@@ -712,7 +616,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -720,11 +624,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
@@ -736,11 +640,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -768,7 +672,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
@@ -776,7 +680,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
@@ -799,83 +703,11 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6733,1560 +6565,12 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1093">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A71" id="1095">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A72" id="1096">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A73" id="1097">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A74" id="1098">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A75" id="1099">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A76" id="1100">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A77" id="1101">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A78" id="1102">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A79" id="1103">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A80" id="1104">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A81" id="1105">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A82" id="1106">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A83" id="1107">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A84" id="1108">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A85" id="1109">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>86</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A86" id="1110">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8372,119 +6656,119 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -8492,199 +6776,199 @@
         <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
@@ -8716,47 +7000,47 @@
         <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>103</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="59">
@@ -8788,15 +7072,15 @@
         <v>116</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -8804,183 +7088,39 @@
         <v>119</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C69" s="1" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -10486,402 +8626,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId71" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId72" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId73" name="A71">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId74" name="A72">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId75" name="A73">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId76" name="A74">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId77" name="A75">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId78" name="A76">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId79" name="A77">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId80" name="A78">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId81" name="A79">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId82" name="A80">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId83" name="A81">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId84" name="A82">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId85" name="A83">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId86" name="A84">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId87" name="A85">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId88" name="A86">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>86</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/PortugueseBrazil.xlsx
+++ b/AAAGameData/Languages/PortugueseBrazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="131">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -399,6 +399,12 @@
   </si>
   <si>
     <t>Agradecemos sua generosa doação!</t>
+  </si>
+  <si>
+    <t>giftHint</t>
+  </si>
+  <si>
+    <t>Colete baús de tesouro</t>
   </si>
 </sst>
 </file>
@@ -703,6 +709,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6565,12 +6575,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -7121,6 +7217,14 @@
       </c>
       <c r="C68" s="1" t="s">
         <v>128</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -8626,6 +8730,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>
